--- a/Empreendimentos.xlsx
+++ b/Empreendimentos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="350">
   <si>
     <t xml:space="preserve">Empreendimento</t>
   </si>
@@ -341,7 +341,7 @@
     <t xml:space="preserve">8milhões e 500mil</t>
   </si>
   <si>
-    <t xml:space="preserve">CASAPIAUI.png</t>
+    <t xml:space="preserve">CASAPIAUI.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Helbor</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">Aguarde Lançamento</t>
   </si>
   <si>
-    <t xml:space="preserve">em-breve.png</t>
+    <t xml:space="preserve">em-breve.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Grand Vivaz Lapa</t>
@@ -619,6 +619,459 @@
   </si>
   <si>
     <t xml:space="preserve">220mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERY FARIA LIMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA CUNHA GAGO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">22M 39M  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 a 2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varanda </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">430mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERYFARIALIMA_ONE.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ONE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERY PEDROSO DE MORAES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA ALVARES YANES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24M A 39 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">355mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERY PEDROSO DE MORAES ONE.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEX ONE ESTAÇÃO CLINICAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA TEODORO SAMPAIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">23M 46M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">409mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLLIE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Dr. Fernandes Coelho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34M A 225M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NR E 3 SUI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varanda e Vaga </t>
+  </si>
+  <si>
+    <t xml:space="preserve">630mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OLLIE_ONE.webp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERITO LAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA BARTOLOMEU PAES - VILA ANASTACIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37M E 38M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO; BEACH TENIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">299mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERITO LAPA.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CURY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTO SÃO DOMINGOS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV MUTINGA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO EXCETO PISCINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">258mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALTO SÃO DOMINGOS CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERITO BARRA FUNDA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV THOMAS EDSON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">34M A 45M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">304mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MERITO BARRA FUNDA CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYNE AGUA BRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA COMENDADOR SOUZA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37M A 47M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">310mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LYNE BARRA FUNDA CURY 2.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA SANTA MARINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA JOSE INACIO DO Rosfiro </t>
+  </si>
+  <si>
+    <t xml:space="preserve">43M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">379mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA SANTA MARINA CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA AGUA BRANCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV JOSE MARIA DE FARIA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37M A 42M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">324mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cidade-Lapa-Agua-Branca_CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA PERDIZES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34M A 46M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">269mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA PERDIZES CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA POMPEIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV JOSE INACIO DO ROSARIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">38M A 45M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">371mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CIDADE LAPA POMPEIA CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astro Santa Marina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV ADRIANO JOSE MARCHINI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">35M A 50M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO E UND C GARDEN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">326mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASTRO SANTA MARINA.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARTE SANTA MARINA  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV SANTA MARINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41M E 44M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">380mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360  PARK VIEW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV DO ANASTACIO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">37M A 46M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">307mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">360 PARK VIEW CURY.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRANOÁ</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rua Marina Ciufuli Zanfelice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36M A 49M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">383mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TERRANOA - ENGELUX.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ENGELUX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LA PARQUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rua Marina Ciufuli Zanfelice,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41 A 55M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 a 3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">426mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO BUTANTÃ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV DO RIO PEQUENO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30M A 44M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Varanda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">264mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MARCO_BUTANTA_ENGELUX.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SP MORUMBI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">R. Comendador Elias Assi, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">27M E 38M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GO LAPA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AV GINO CESARO </t>
+  </si>
+  <si>
+    <t xml:space="preserve">54M A 69M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">594mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GO LAPA - ECON.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECON</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPIC JAGUARE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA AUTÁS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">59M A 69</t>
+  </si>
+  <si>
+    <t xml:space="preserve">541mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EPIC JAGUARE - ECON.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPE STYLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA BAUMANN VILA LEOPOLDINA </t>
+  </si>
+  <si>
+    <t xml:space="preserve">29M A 43M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPE STYLE ECON.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPE TREND</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA BAUMANN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">76M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMPLETO - BEACH TENNIS </t>
+  </si>
+  <si>
+    <t xml:space="preserve">989mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HYPE TREND ECON.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OAZII BY PIERO LISSONI </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA SALES JUNIOR </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 173M 212M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 a 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEGRA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPERE BROOKLIN </t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA ANDRE AMPERE </t>
+  </si>
+  <si>
+    <t xml:space="preserve">262M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4milhão e 854mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMPERE BROOKLIN TEGRA.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDIOS BERRINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUA ARANDU </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">554mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STUDIOS BERRINI TEGRA.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPITOLO BY PIERO LISSONI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Ibaragui Nissui</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2120M E 363M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">4milhão e 625mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAPITOLIO TEGRA.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOZAE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rua Conselheiro Brotero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46M E 73M </t>
+  </si>
+  <si>
+    <t xml:space="preserve">896mil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MOZAE TEGRA.jpg</t>
   </si>
 </sst>
 </file>
@@ -631,7 +1084,7 @@
     <numFmt numFmtId="166" formatCode="#,##0.00"/>
     <numFmt numFmtId="167" formatCode="[$R$-416]\ #,##0.00;[RED]\-[$R$-416]\ #,##0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -684,13 +1137,39 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC9211E"/>
+      <name val="Calibri"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFC9211E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -776,100 +1255,140 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -936,7 +1455,7 @@
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FFC9211E"/>
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF1F1F1F"/>
@@ -1122,14 +1641,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K1048576"/>
+  <dimension ref="A1:Z991"/>
   <sheetFormatPr defaultColWidth="14.43359375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="30.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="21.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="33.79"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="20.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="32.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="11.4"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="45.43"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="51.74"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="18.43"/>
@@ -2112,7 +2631,7 @@
       <c r="I28" s="17" t="n">
         <v>47088</v>
       </c>
-      <c r="J28" s="23" t="s">
+      <c r="J28" s="24" t="s">
         <v>176</v>
       </c>
       <c r="K28" s="18" t="s">
@@ -2259,106 +2778,995 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I33" s="8"/>
+    <row r="33" s="27" customFormat="true" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25"/>
+      <c r="B33" s="25"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="25"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
+      <c r="G33" s="25"/>
+      <c r="H33" s="25"/>
+      <c r="I33" s="26"/>
+      <c r="J33" s="25"/>
+      <c r="K33" s="25"/>
+      <c r="L33" s="25"/>
+      <c r="M33" s="25"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="25"/>
+      <c r="P33" s="25"/>
+      <c r="Q33" s="25"/>
+      <c r="R33" s="25"/>
+      <c r="S33" s="25"/>
+      <c r="T33" s="25"/>
+      <c r="U33" s="25"/>
+      <c r="V33" s="25"/>
+      <c r="W33" s="25"/>
+      <c r="X33" s="25"/>
+      <c r="Y33" s="25"/>
+      <c r="Z33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I34" s="8"/>
+      <c r="A34" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="D34" s="29" t="s">
+        <v>201</v>
+      </c>
+      <c r="E34" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F34" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G34" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I34" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="K34" s="30" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I35" s="8"/>
+      <c r="A35" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="B35" s="28"/>
+      <c r="C35" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="D35" s="29" t="s">
+        <v>210</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G35" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="I35" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="K35" s="30" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I36" s="8"/>
+      <c r="A36" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="28"/>
+      <c r="C36" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="29" t="s">
+        <v>215</v>
+      </c>
+      <c r="E36" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G36" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="I36" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J36" s="29" t="s">
+        <v>193</v>
+      </c>
+      <c r="K36" s="30" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I37" s="8"/>
+      <c r="A37" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B37" s="28"/>
+      <c r="C37" s="29" t="s">
+        <v>218</v>
+      </c>
+      <c r="D37" s="29" t="s">
+        <v>219</v>
+      </c>
+      <c r="E37" s="29" t="s">
+        <v>220</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G37" s="30" t="s">
+        <v>204</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="I37" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="K37" s="30" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0"/>
+      <c r="C38" s="29"/>
+      <c r="D38" s="29"/>
+      <c r="E38" s="29"/>
+      <c r="F38" s="9"/>
+      <c r="G38" s="30"/>
       <c r="I38" s="8"/>
+      <c r="K38" s="30"/>
     </row>
     <row r="39" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I39" s="8"/>
+      <c r="A39" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="B39" s="28"/>
+      <c r="C39" s="29" t="s">
+        <v>225</v>
+      </c>
+      <c r="D39" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="E39" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F39" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="I39" s="31" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J39" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="K39" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I40" s="8"/>
+      <c r="A40" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="B40" s="28"/>
+      <c r="C40" s="29" t="s">
+        <v>232</v>
+      </c>
+      <c r="D40" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="E40" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F40" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>234</v>
+      </c>
+      <c r="H40" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="I40" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J40" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="K40" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I41" s="8"/>
+      <c r="A41" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B41" s="28"/>
+      <c r="C41" s="29" t="s">
+        <v>238</v>
+      </c>
+      <c r="D41" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="E41" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F41" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>240</v>
+      </c>
+      <c r="H41" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I41" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J41" s="28" t="s">
+        <v>242</v>
+      </c>
+      <c r="K41" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I42" s="8"/>
+      <c r="A42" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="B42" s="28"/>
+      <c r="C42" s="29" t="s">
+        <v>244</v>
+      </c>
+      <c r="D42" s="29" t="s">
+        <v>245</v>
+      </c>
+      <c r="E42" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F42" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G42" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="I42" s="31" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J42" s="28" t="s">
+        <v>248</v>
+      </c>
+      <c r="K42" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I43" s="8"/>
+      <c r="A43" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="B43" s="28"/>
+      <c r="C43" s="32" t="s">
+        <v>250</v>
+      </c>
+      <c r="D43" s="29" t="s">
+        <v>251</v>
+      </c>
+      <c r="E43" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="I43" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K43" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I44" s="8"/>
+      <c r="A44" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="B44" s="28"/>
+      <c r="C44" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="D44" s="29" t="s">
+        <v>256</v>
+      </c>
+      <c r="E44" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F44" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I44" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K44" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I45" s="8"/>
+      <c r="A45" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="B45" s="28"/>
+      <c r="C45" s="29" t="s">
+        <v>255</v>
+      </c>
+      <c r="D45" s="29" t="s">
+        <v>260</v>
+      </c>
+      <c r="E45" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="H45" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I45" s="33" t="n">
+        <v>2029</v>
+      </c>
+      <c r="J45" s="28" t="s">
+        <v>262</v>
+      </c>
+      <c r="K45" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="46" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I46" s="8"/>
+      <c r="A46" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="B46" s="28"/>
+      <c r="C46" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="D46" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="E46" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F46" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I46" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="K46" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="47" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I47" s="8"/>
+      <c r="A47" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B47" s="28"/>
+      <c r="C47" s="32" t="s">
+        <v>269</v>
+      </c>
+      <c r="D47" s="29" t="s">
+        <v>270</v>
+      </c>
+      <c r="E47" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F47" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>271</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="I47" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K47" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I48" s="8"/>
+      <c r="A48" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B48" s="28"/>
+      <c r="C48" s="29" t="s">
+        <v>275</v>
+      </c>
+      <c r="D48" s="29" t="s">
+        <v>276</v>
+      </c>
+      <c r="E48" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="I48" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J48" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="K48" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="49" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I49" s="8"/>
+      <c r="A49" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B49" s="28"/>
+      <c r="C49" s="29" t="s">
+        <v>279</v>
+      </c>
+      <c r="D49" s="29" t="s">
+        <v>280</v>
+      </c>
+      <c r="E49" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I49" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J49" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="K49" s="30" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="0"/>
+      <c r="C50" s="0"/>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+      <c r="G50" s="0"/>
       <c r="I50" s="8"/>
     </row>
     <row r="51" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I51" s="8"/>
+      <c r="A51" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="B51" s="28"/>
+      <c r="C51" s="29" t="s">
+        <v>284</v>
+      </c>
+      <c r="D51" s="29" t="s">
+        <v>285</v>
+      </c>
+      <c r="E51" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F51" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I51" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="K51" s="30" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I52" s="8"/>
+      <c r="A52" s="1" t="s">
+        <v>289</v>
+      </c>
+      <c r="B52" s="28"/>
+      <c r="C52" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="D52" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="E52" s="29" t="s">
+        <v>292</v>
+      </c>
+      <c r="F52" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="G52" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>293</v>
+      </c>
+      <c r="I52" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="J52" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="K52" s="30" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I53" s="8"/>
+      <c r="A53" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B53" s="28"/>
+      <c r="C53" s="29" t="s">
+        <v>295</v>
+      </c>
+      <c r="D53" s="29" t="s">
+        <v>296</v>
+      </c>
+      <c r="E53" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F53" s="9" t="s">
+        <v>297</v>
+      </c>
+      <c r="G53" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I53" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J53" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="K53" s="30" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I54" s="8"/>
+      <c r="A54" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B54" s="28"/>
+      <c r="C54" s="29" t="s">
+        <v>301</v>
+      </c>
+      <c r="D54" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="E54" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F54" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G54" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H54" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J54" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="K54" s="30" t="s">
+        <v>288</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="0"/>
+      <c r="C55" s="0"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="G55" s="0"/>
       <c r="I55" s="8"/>
     </row>
     <row r="56" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I56" s="8"/>
+      <c r="A56" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B56" s="28"/>
+      <c r="C56" s="29" t="s">
+        <v>304</v>
+      </c>
+      <c r="D56" s="29" t="s">
+        <v>305</v>
+      </c>
+      <c r="E56" s="29" t="n">
+        <v>2</v>
+      </c>
+      <c r="F56" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H56" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="I56" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J56" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="K56" s="30" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="57" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I57" s="8"/>
+      <c r="A57" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="B57" s="28"/>
+      <c r="C57" s="29" t="s">
+        <v>310</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>311</v>
+      </c>
+      <c r="E57" s="29" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H57" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="I57" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J57" s="28" t="s">
+        <v>313</v>
+      </c>
+      <c r="K57" s="30" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="58" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I58" s="8"/>
+      <c r="A58" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="B58" s="28"/>
+      <c r="C58" s="29" t="s">
+        <v>315</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="E58" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="F58" s="9" t="s">
+        <v>203</v>
+      </c>
+      <c r="G58" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H58" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="I58" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J58" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="K58" s="30" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I59" s="8"/>
+      <c r="A59" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="B59" s="28"/>
+      <c r="C59" s="29" t="s">
+        <v>319</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>320</v>
+      </c>
+      <c r="E59" s="29" t="n">
+        <v>3</v>
+      </c>
+      <c r="F59" s="9" t="s">
+        <v>221</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>321</v>
+      </c>
+      <c r="H59" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="I59" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J59" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="K59" s="30" t="s">
+        <v>308</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="0"/>
+      <c r="C60" s="0"/>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="G60" s="0"/>
       <c r="I60" s="8"/>
     </row>
     <row r="61" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I61" s="8"/>
+      <c r="A61" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B61" s="28"/>
+      <c r="C61" s="29" t="s">
+        <v>325</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>326</v>
+      </c>
+      <c r="E61" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="F61" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H61" s="29" t="s">
+        <v>192</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="J61" s="32" t="s">
+        <v>193</v>
+      </c>
+      <c r="K61" s="30" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="62" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I62" s="8"/>
+      <c r="A62" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="B62" s="28"/>
+      <c r="C62" s="29" t="s">
+        <v>330</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="E62" s="29" t="n">
+        <v>4</v>
+      </c>
+      <c r="F62" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H62" s="29" t="s">
+        <v>332</v>
+      </c>
+      <c r="I62" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J62" s="28" t="s">
+        <v>333</v>
+      </c>
+      <c r="K62" s="30" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I63" s="8"/>
+      <c r="A63" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="B63" s="28"/>
+      <c r="C63" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="D63" s="29" t="s">
+        <v>336</v>
+      </c>
+      <c r="E63" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="F63" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I63" s="31" t="n">
+        <v>2027</v>
+      </c>
+      <c r="J63" s="28" t="s">
+        <v>339</v>
+      </c>
+      <c r="K63" s="30" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="64" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I64" s="8"/>
+      <c r="A64" s="1" t="s">
+        <v>340</v>
+      </c>
+      <c r="B64" s="28"/>
+      <c r="C64" s="29" t="s">
+        <v>341</v>
+      </c>
+      <c r="D64" s="29" t="s">
+        <v>342</v>
+      </c>
+      <c r="E64" s="29" t="s">
+        <v>327</v>
+      </c>
+      <c r="F64" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H64" s="29" t="s">
+        <v>343</v>
+      </c>
+      <c r="I64" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J64" s="28" t="s">
+        <v>344</v>
+      </c>
+      <c r="K64" s="30" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="I65" s="8"/>
+      <c r="A65" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="B65" s="28"/>
+      <c r="C65" s="29" t="s">
+        <v>346</v>
+      </c>
+      <c r="D65" s="29" t="s">
+        <v>347</v>
+      </c>
+      <c r="E65" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="F65" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>246</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="I65" s="31" t="n">
+        <v>2028</v>
+      </c>
+      <c r="J65" s="28" t="s">
+        <v>349</v>
+      </c>
+      <c r="K65" s="30" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="66" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C66" s="0"/>
+      <c r="F66" s="29"/>
       <c r="I66" s="8"/>
     </row>
     <row r="67" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5133,7 +6541,9 @@
     <row r="990" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="I990" s="8"/>
     </row>
-    <row r="1048576" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="991" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="I991" s="8"/>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
